--- a/Result/profitability/3543.xlsx
+++ b/Result/profitability/3543.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2375</v>
+        <v>-0.2225</v>
       </c>
       <c r="N2" t="n">
-        <v>11.2825</v>
+        <v>11.3325</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10625</v>
+        <v>-0.1125</v>
       </c>
       <c r="N3" t="n">
-        <v>11.51625</v>
+        <v>11.13875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2887500000000001</v>
+        <v>0.23</v>
       </c>
       <c r="N4" t="n">
-        <v>12.6</v>
+        <v>12.3125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8650000000000001</v>
+        <v>0.8812500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>14.02625</v>
+        <v>13.95125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.245</v>
+        <v>1.29</v>
       </c>
       <c r="N6" t="n">
-        <v>14.68875</v>
+        <v>15.18875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6875</v>
+        <v>1.775</v>
       </c>
       <c r="N7" t="n">
-        <v>16.20875</v>
+        <v>16.97</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7163,6 +7163,133 @@
       </c>
       <c r="AM53" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>827</v>
+      </c>
+      <c r="D54" t="n">
+        <v>730</v>
+      </c>
+      <c r="E54" t="n">
+        <v>97</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-6.37%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>27</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-42</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-0.45125</v>
+      </c>
+      <c r="N54" t="n">
+        <v>10.85125</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.2444208289054199</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-0.2549019607843137</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>-0.04874086108854592</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
